--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260609.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.44%</t>
+          <t>12.24%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.60%</t>
+          <t>10.20%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.31%</t>
+          <t>9.27%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>7.38%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.57%</t>
+          <t>5.58%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.09%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>21,103</t>
+          <t>9,932</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>9,932</t>
+          <t>21,103</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -946,24 +946,24 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>15,048</t>
+          <t>51,099</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,22 +975,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>51,099</t>
+          <t>15,048</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1012,24 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>18,120</t>
+          <t>53,029</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>53,029</t>
+          <t>18,120</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,66 +1063,66 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>54,509</t>
+          <t>34,552</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>14,428</t>
+          <t>54,509</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>34,552</t>
+          <t>14,428</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>14,370</t>
+          <t>129,716</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>129,716</t>
+          <t>14,370</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>61,358</t>
+          <t>78,607</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>78,607</t>
+          <t>61,358</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1437,44 +1437,44 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>ENPH US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Enphase能源公司</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>31,476</t>
+          <t>16,932</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>ENPH US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>Enphase能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>16,932</t>
+          <t>31,476</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>77,540</t>
+          <t>29,949</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,61 +1569,61 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>29,949</t>
+          <t>77,540</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>75,391</t>
+          <t>8,750</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>8,750</t>
+          <t>75,391</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,39 +1635,39 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>AMSC US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>美國超導公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>21,740</t>
+          <t>10,741</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>AMSC US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>美國超導公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>10,741</t>
+          <t>21,740</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.02%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>163,648,032</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
